--- a/survey_templates/044_fabric_color_poll--survey_templates.xlsx
+++ b/survey_templates/044_fabric_color_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -926,12 +926,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medium_weight</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium weight</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -943,29 +943,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Soft</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>favorite_fabric_texture_1_choices</t>
+          <t>favorite_fabric_weave_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>soft</t>
+          <t>tight_weave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Tight weave</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tight_weave</t>
+          <t>medium_weave</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tight weave</t>
+          <t>Medium weave</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medium_weave</t>
+          <t>loose_weave</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medium weave</t>
+          <t>Loose weave</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>loose_weave</t>
+          <t>plush</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loose weave</t>
+          <t>Plush</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plush</t>
+          <t>smooth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plush</t>
+          <t>Smooth</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>smooth</t>
+          <t>herringbone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Smooth</t>
+          <t>Herringbone</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>herringbone</t>
+          <t>chenille</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Herringbone</t>
+          <t>Chenille</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>chenille</t>
+          <t>twill</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chenille</t>
+          <t>Twill</t>
         </is>
       </c>
     </row>
@@ -1096,29 +1096,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>twill</t>
+          <t>twill_tape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Twill</t>
+          <t>Twill tape</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>favorite_fabric_weave_1_choices</t>
+          <t>favorite_fabric_weight_1_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>twill_tape</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Twill tape</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1164,27 +1164,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>extremely_light</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>favorite_fabric_weight_1_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>extremely_light</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Extremely light</t>
         </is>
